--- a/public/exports-from-60-with-coowners/29189706.xlsx
+++ b/public/exports-from-60-with-coowners/29189706.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505577</t>
+          <t xml:space="preserve">311505582</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311597138</t>
+          <t xml:space="preserve">311597142</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189706.xlsx
+++ b/public/exports-from-60-with-coowners/29189706.xlsx
@@ -4564,7 +4564,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505582</t>
+          <t xml:space="preserve">311505577</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189706.xlsx
+++ b/public/exports-from-60-with-coowners/29189706.xlsx
@@ -9664,7 +9664,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311597142</t>
+          <t xml:space="preserve">311597138</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
